--- a/hardware/battery-capacity-tests_lithium-ion_AA-AAA.xlsx
+++ b/hardware/battery-capacity-tests_lithium-ion_AA-AAA.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcava\Documents\GitHub\Coding\hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D03A13A4-1AF4-42EB-B332-677209C6355C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{501EBCB3-B332-4D14-81FA-41B103AFA92A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1665" windowWidth="38490" windowHeight="15330" xr2:uid="{E5D7BF72-F0C5-4096-89C0-8DC37475FB76}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="38700" windowHeight="15345" xr2:uid="{E5D7BF72-F0C5-4096-89C0-8DC37475FB76}"/>
   </bookViews>
   <sheets>
     <sheet name="AA Batteries" sheetId="4" r:id="rId1"/>
     <sheet name="AAA Batteries" sheetId="3" r:id="rId2"/>
+    <sheet name="Guide" sheetId="5" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="42">
   <si>
     <t>Cutoff</t>
   </si>
@@ -137,6 +138,33 @@
   </si>
   <si>
     <t>Form Factor</t>
+  </si>
+  <si>
+    <t>2. Connect battery terminal to HW-586</t>
+  </si>
+  <si>
+    <t>3. Insert battery to be tested into battery terminal</t>
+  </si>
+  <si>
+    <t>Battery testing AA/AAA (or other 1.5V) batteries using HW-586 Module</t>
+  </si>
+  <si>
+    <t>1. Connect resistance to HW-586 which causes the module to push ~0.35 Amps during testing (two of the white block resistors included with HW-586 wired in parallel should do)</t>
+  </si>
+  <si>
+    <t>4. Plug a Micro USB cable into the HW-586 module, connect the other end of the cable into a USB power source and the HW-586 should power on</t>
+  </si>
+  <si>
+    <t>5. Press "+" sign until "P00.8" is shown on the HW-586's screen (denotes a cutoff voltage of 0.8V)</t>
+  </si>
+  <si>
+    <t>6. Press "OK" to confirm the cutoff voltage and the HW-586 will run until the battery reaches 0.8V</t>
+  </si>
+  <si>
+    <t>7. Once test is complete, wait for the "Ah" (Amp-hours) LED on the HW-586 to light up, then save its associated value into spreadsheet or other record keeping location</t>
+  </si>
+  <si>
+    <t>e-CIRCUIT</t>
   </si>
 </sst>
 </file>
@@ -146,7 +174,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0&quot; mAh&quot;"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -154,13 +182,31 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Fira Code Retina"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Fira Code Retina"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -184,7 +230,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -195,6 +241,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -338,9 +387,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -378,7 +427,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -484,7 +533,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -626,7 +675,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -920,19 +969,31 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
+      <c r="A8" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
+      <c r="C8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
       <c r="L8" s="1" t="str">
         <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
         <v/>
@@ -1609,19 +1670,31 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
+      <c r="A9" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
+      <c r="C9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
       <c r="L9" s="1" t="str">
         <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
         <v/>
@@ -1950,4 +2023,70 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E3D4079-DC30-422D-A8A8-08ECD8BF2C74}">
+  <dimension ref="A1:A20"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="231.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="9.140625" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" s="7" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="18" s="7" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="19" s="7" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="20" s="7" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/hardware/battery-capacity-tests_lithium-ion_AA-AAA.xlsx
+++ b/hardware/battery-capacity-tests_lithium-ion_AA-AAA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcava\Documents\GitHub\Coding\hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{501EBCB3-B332-4D14-81FA-41B103AFA92A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E60155C7-F328-4CB7-AF0B-0381D9B7B9DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="38700" windowHeight="15345" xr2:uid="{E5D7BF72-F0C5-4096-89C0-8DC37475FB76}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{E5D7BF72-F0C5-4096-89C0-8DC37475FB76}"/>
   </bookViews>
   <sheets>
     <sheet name="AA Batteries" sheetId="4" r:id="rId1"/>
@@ -38,10 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="42">
-  <si>
-    <t>Cutoff</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="49">
   <si>
     <t>EBL</t>
   </si>
@@ -67,9 +64,6 @@
     <t>AAA</t>
   </si>
   <si>
-    <t>Current</t>
-  </si>
-  <si>
     <t>KILISTEELS</t>
   </si>
   <si>
@@ -118,63 +112,99 @@
     <t>LANKOO</t>
   </si>
   <si>
-    <t>Capacity
+    <t>Battery Brand</t>
+  </si>
+  <si>
+    <t>Form Factor</t>
+  </si>
+  <si>
+    <t>2. Connect battery terminal to HW-586</t>
+  </si>
+  <si>
+    <t>3. Insert battery to be tested into battery terminal</t>
+  </si>
+  <si>
+    <t>Battery testing AA/AAA (or other 1.5V) batteries using HW-586 Module</t>
+  </si>
+  <si>
+    <t>1. Connect resistance to HW-586 which causes the module to push ~0.35 Amps during testing (two of the white block resistors included with HW-586 wired in parallel should do)</t>
+  </si>
+  <si>
+    <t>4. Plug a Micro USB cable into the HW-586 module, connect the other end of the cable into a USB power source and the HW-586 should power on</t>
+  </si>
+  <si>
+    <t>5. Press "+" sign until "P00.8" is shown on the HW-586's screen (denotes a cutoff voltage of 0.8V)</t>
+  </si>
+  <si>
+    <t>6. Press "OK" to confirm the cutoff voltage and the HW-586 will run until the battery reaches 0.8V</t>
+  </si>
+  <si>
+    <t>e-CIRCUIT</t>
+  </si>
+  <si>
+    <t>7. Once test is complete, the HW-586 will bleak rapidly, displaying the "Ah" (Amp-hours) result - Save this into desired spreadsheet or other record keeping location</t>
+  </si>
+  <si>
+    <t>Package Quantity</t>
+  </si>
+  <si>
+    <t>Capacity (mAh)
+(Test #1)</t>
+  </si>
+  <si>
+    <t>Capacity (mAh)
+(Test #2)</t>
+  </si>
+  <si>
+    <t>Capacity (mAh)
+(Test #3)</t>
+  </si>
+  <si>
+    <t>Capacity (mAh)
+(Test #4)</t>
+  </si>
+  <si>
+    <t>Capacity (mAh)
 (Averaged)</t>
   </si>
   <si>
-    <t>Capacity (Test #1)</t>
-  </si>
-  <si>
-    <t>Capacity (Test #2)</t>
-  </si>
-  <si>
-    <t>Capacity (Test #3)</t>
-  </si>
-  <si>
-    <t>Capacity (Test #4)</t>
-  </si>
-  <si>
-    <t>Battery Brand</t>
-  </si>
-  <si>
-    <t>Form Factor</t>
-  </si>
-  <si>
-    <t>2. Connect battery terminal to HW-586</t>
-  </si>
-  <si>
-    <t>3. Insert battery to be tested into battery terminal</t>
-  </si>
-  <si>
-    <t>Battery testing AA/AAA (or other 1.5V) batteries using HW-586 Module</t>
-  </si>
-  <si>
-    <t>1. Connect resistance to HW-586 which causes the module to push ~0.35 Amps during testing (two of the white block resistors included with HW-586 wired in parallel should do)</t>
-  </si>
-  <si>
-    <t>4. Plug a Micro USB cable into the HW-586 module, connect the other end of the cable into a USB power source and the HW-586 should power on</t>
-  </si>
-  <si>
-    <t>5. Press "+" sign until "P00.8" is shown on the HW-586's screen (denotes a cutoff voltage of 0.8V)</t>
-  </si>
-  <si>
-    <t>6. Press "OK" to confirm the cutoff voltage and the HW-586 will run until the battery reaches 0.8V</t>
-  </si>
-  <si>
-    <t>7. Once test is complete, wait for the "Ah" (Amp-hours) LED on the HW-586 to light up, then save its associated value into spreadsheet or other record keeping location</t>
-  </si>
-  <si>
-    <t>e-CIRCUIT</t>
+    <t>Package Price
+($)</t>
+  </si>
+  <si>
+    <t>Price per battery
+($)</t>
+  </si>
+  <si>
+    <t>Cutoff
+(V)</t>
+  </si>
+  <si>
+    <t>Current
+(A)</t>
+  </si>
+  <si>
+    <t>Capacity per Dollar (mAh)</t>
+  </si>
+  <si>
+    <t>Chemistry</t>
+  </si>
+  <si>
+    <t>Alkaline</t>
+  </si>
+  <si>
+    <t>Lithium Ion</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0&quot; mAh&quot;"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -194,19 +224,21 @@
       <color theme="1"/>
       <name val="Fira Code Retina"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -230,7 +262,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -243,12 +275,34 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
+  <dxfs count="24">
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0&quot; mAh&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="0&quot; mAh&quot;"/>
     </dxf>
@@ -277,7 +331,44 @@
       </border>
     </dxf>
     <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="dotted">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0&quot; mAh&quot;"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="dotted">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0&quot; mAh&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="0&quot; mAh&quot;"/>
@@ -335,25 +426,39 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{BAEE4FAC-F828-4C69-BD4B-209D42AC9A11}" name="Table35" displayName="Table35" ref="A1:L25" totalsRowShown="0" headerRowDxfId="13">
-  <autoFilter ref="A1:L25" xr:uid="{9D7B16C1-0AF6-47A8-A5C4-2FD9C768AE5C}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L25">
-    <sortCondition ref="B1:B25"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{BAEE4FAC-F828-4C69-BD4B-209D42AC9A11}" name="Table35" displayName="Table35" ref="A1:Q25" totalsRowShown="0" headerRowDxfId="23">
+  <autoFilter ref="A1:Q25" xr:uid="{9D7B16C1-0AF6-47A8-A5C4-2FD9C768AE5C}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q25">
+    <sortCondition ref="M1:M25"/>
   </sortState>
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{CBABFE4A-DB4B-478A-A196-6B10725888CE}" name="Battery Brand" dataDxfId="12"/>
+  <tableColumns count="17">
+    <tableColumn id="1" xr3:uid="{CBABFE4A-DB4B-478A-A196-6B10725888CE}" name="Battery Brand" dataDxfId="22"/>
     <tableColumn id="2" xr3:uid="{A4C15DEC-98CA-4B4A-AA6D-9D8629196B6D}" name="Form Factor"/>
+    <tableColumn id="18" xr3:uid="{5C2654CB-3147-4CBC-B035-883A9090E4E6}" name="Chemistry" dataDxfId="12"/>
     <tableColumn id="3" xr3:uid="{C5D6165E-2DC1-490A-8745-775A230CE959}" name="Plug Loc"/>
     <tableColumn id="4" xr3:uid="{76E5C7FE-A9FC-4892-AA2F-F4BDBC0FE43E}" name="USB Type"/>
     <tableColumn id="5" xr3:uid="{0B30B98B-6A8B-4BC5-AAA4-52D69388E8A1}" name="Splitter Incl."/>
-    <tableColumn id="6" xr3:uid="{679FA49F-E3B8-466B-A769-C279FED07A47}" name="Cutoff"/>
-    <tableColumn id="7" xr3:uid="{0749C5D5-9FE3-4320-A646-E78C6602DB2D}" name="Current"/>
-    <tableColumn id="8" xr3:uid="{FC5DC19F-46DB-49F0-B6EB-F8D8DFCC5119}" name="Capacity (Test #1)" dataDxfId="11"/>
-    <tableColumn id="9" xr3:uid="{2C2758A8-2AF5-47E7-BF85-99A3D8B3BA30}" name="Capacity (Test #2)" dataDxfId="10"/>
-    <tableColumn id="10" xr3:uid="{33DF939F-2A16-4823-AACA-AC4D2782FCC1}" name="Capacity (Test #3)" dataDxfId="9"/>
-    <tableColumn id="11" xr3:uid="{DD1EEECD-4600-48C0-A802-DB79834A7A50}" name="Capacity (Test #4)" dataDxfId="8"/>
-    <tableColumn id="12" xr3:uid="{815B7A98-D189-4530-8370-36E96E9386A8}" name="Capacity_x000a_(Averaged)" dataDxfId="7">
-      <calculatedColumnFormula>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</calculatedColumnFormula>
+    <tableColumn id="6" xr3:uid="{679FA49F-E3B8-466B-A769-C279FED07A47}" name="Cutoff_x000a_(V)"/>
+    <tableColumn id="7" xr3:uid="{0749C5D5-9FE3-4320-A646-E78C6602DB2D}" name="Current_x000a_(A)"/>
+    <tableColumn id="8" xr3:uid="{FC5DC19F-46DB-49F0-B6EB-F8D8DFCC5119}" name="Capacity (mAh)_x000a_(Test #1)" dataDxfId="21"/>
+    <tableColumn id="9" xr3:uid="{2C2758A8-2AF5-47E7-BF85-99A3D8B3BA30}" name="Capacity (mAh)_x000a_(Test #2)" dataDxfId="20"/>
+    <tableColumn id="10" xr3:uid="{33DF939F-2A16-4823-AACA-AC4D2782FCC1}" name="Capacity (mAh)_x000a_(Test #3)" dataDxfId="19"/>
+    <tableColumn id="11" xr3:uid="{DD1EEECD-4600-48C0-A802-DB79834A7A50}" name="Capacity (mAh)_x000a_(Test #4)" dataDxfId="18"/>
+    <tableColumn id="12" xr3:uid="{815B7A98-D189-4530-8370-36E96E9386A8}" name="Capacity (mAh)_x000a_(Averaged)" dataDxfId="17">
+      <calculatedColumnFormula>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="13" xr3:uid="{FB50ABF7-3A80-4E6B-B421-533E61A624AE}" name="Package Quantity" dataDxfId="16"/>
+    <tableColumn id="14" xr3:uid="{BAAC862F-FE09-469C-B505-5B1D17C687E4}" name="Package Price_x000a_($)" dataDxfId="15"/>
+    <tableColumn id="15" xr3:uid="{4DAA5FFD-D836-4119-968C-53A1BFEA75AC}" name="Price per battery_x000a_($)" dataDxfId="14">
+      <calculatedColumnFormula>IFERROR(Table35[[#This Row],[Package Price
+($)]]/Table35[[#This Row],[Package Quantity]],"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="16" xr3:uid="{B90ADC68-DA10-4B4A-816B-714216F488CF}" name="Capacity per Dollar (mAh)" dataDxfId="13">
+      <calculatedColumnFormula>IFERROR(Table35[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table35[[#This Row],[Price per battery
+($)]],"")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -361,25 +466,39 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D7B16C1-0AF6-47A8-A5C4-2FD9C768AE5C}" name="Table3" displayName="Table3" ref="A1:L25" totalsRowShown="0" headerRowDxfId="6">
-  <autoFilter ref="A1:L25" xr:uid="{9D7B16C1-0AF6-47A8-A5C4-2FD9C768AE5C}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L25">
-    <sortCondition ref="B1:B25"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D7B16C1-0AF6-47A8-A5C4-2FD9C768AE5C}" name="Table3" displayName="Table3" ref="A1:Q25" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A1:Q25" xr:uid="{9D7B16C1-0AF6-47A8-A5C4-2FD9C768AE5C}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M25">
+    <sortCondition ref="M1:M25"/>
   </sortState>
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{5FD88E0E-EEC4-45EA-829E-F14B958619D1}" name="Battery Brand" dataDxfId="5"/>
+  <tableColumns count="17">
+    <tableColumn id="1" xr3:uid="{5FD88E0E-EEC4-45EA-829E-F14B958619D1}" name="Battery Brand" dataDxfId="10"/>
     <tableColumn id="2" xr3:uid="{F0B5B50C-ECE4-4B5B-BC33-E41ECF72CB84}" name="Form Factor"/>
+    <tableColumn id="18" xr3:uid="{C6B4CF7F-2783-48EF-834F-E855B8EEFC07}" name="Chemistry" dataDxfId="9"/>
     <tableColumn id="3" xr3:uid="{95C6D9E4-D9F2-41C1-B5B8-D5C12AADD7D5}" name="Plug Loc"/>
     <tableColumn id="4" xr3:uid="{CC6956E7-B2BF-4E3E-AFF8-F43E275B8834}" name="USB Type"/>
     <tableColumn id="5" xr3:uid="{DAF5776A-02B6-4652-BB4E-D674B4D5241F}" name="Splitter Incl."/>
-    <tableColumn id="6" xr3:uid="{C3CDCA6E-9575-4DE4-83C5-1379AF569F68}" name="Cutoff"/>
-    <tableColumn id="7" xr3:uid="{E0DF1034-A579-4CD7-B7E4-A3A74917FD27}" name="Current"/>
-    <tableColumn id="8" xr3:uid="{DDF1ED42-4BB3-47E1-8105-E90AD843ECD1}" name="Capacity (Test #1)" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{2C98A263-D4F3-4057-9C06-F22A950F7DBA}" name="Capacity (Test #2)" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{5361E4DF-E5D4-4566-BA3C-A08A8A66D480}" name="Capacity (Test #3)" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{5D1D0FB3-8458-4FF6-B2DE-E36C691CFEAE}" name="Capacity (Test #4)" dataDxfId="1"/>
-    <tableColumn id="12" xr3:uid="{63DC296B-3655-4FB6-BD00-EF6D486577A7}" name="Capacity_x000a_(Averaged)" dataDxfId="0">
-      <calculatedColumnFormula>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</calculatedColumnFormula>
+    <tableColumn id="6" xr3:uid="{C3CDCA6E-9575-4DE4-83C5-1379AF569F68}" name="Cutoff_x000a_(V)"/>
+    <tableColumn id="7" xr3:uid="{E0DF1034-A579-4CD7-B7E4-A3A74917FD27}" name="Current_x000a_(A)"/>
+    <tableColumn id="8" xr3:uid="{DDF1ED42-4BB3-47E1-8105-E90AD843ECD1}" name="Capacity (mAh)_x000a_(Test #1)" dataDxfId="8"/>
+    <tableColumn id="9" xr3:uid="{2C98A263-D4F3-4057-9C06-F22A950F7DBA}" name="Capacity (mAh)_x000a_(Test #2)" dataDxfId="7"/>
+    <tableColumn id="10" xr3:uid="{5361E4DF-E5D4-4566-BA3C-A08A8A66D480}" name="Capacity (mAh)_x000a_(Test #3)" dataDxfId="6"/>
+    <tableColumn id="11" xr3:uid="{5D1D0FB3-8458-4FF6-B2DE-E36C691CFEAE}" name="Capacity (mAh)_x000a_(Test #4)" dataDxfId="5"/>
+    <tableColumn id="12" xr3:uid="{63DC296B-3655-4FB6-BD00-EF6D486577A7}" name="Capacity (mAh)_x000a_(Averaged)" dataDxfId="4">
+      <calculatedColumnFormula>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="13" xr3:uid="{B4A9F974-E29B-41F4-8269-54197CFA3C31}" name="Package Quantity" dataDxfId="3"/>
+    <tableColumn id="14" xr3:uid="{71EB4A3B-A497-47F8-9502-BC8C4453702F}" name="Package Price_x000a_($)" dataDxfId="2"/>
+    <tableColumn id="15" xr3:uid="{3971A6B9-1C45-48AC-BFEB-B8DE558BE4BF}" name="Price per battery_x000a_($)" dataDxfId="1">
+      <calculatedColumnFormula>IFERROR(Table3[[#This Row],[Package Price
+($)]]/Table3[[#This Row],[Package Quantity]],"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="16" xr3:uid="{28FCF180-4137-4956-B227-BA4FC12BB9E1}" name="Capacity per Dollar (mAh)" dataDxfId="0">
+      <calculatedColumnFormula>IFERROR(Table3[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table3[[#This Row],[Price per battery
+($)]],"")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -683,647 +802,1067 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07B88473-F5AD-4E7A-8759-03380A4A5160}">
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.85546875" customWidth="1"/>
-    <col min="4" max="4" width="7.5703125" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.85546875" customWidth="1"/>
+    <col min="5" max="5" width="7.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11" style="8" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.5703125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>27</v>
+        <v>43</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="P1" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>20</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="3">
+        <v>201</v>
+      </c>
+      <c r="J2" s="3">
+        <v>304</v>
+      </c>
+      <c r="K2" s="3">
+        <v>358</v>
+      </c>
+      <c r="L2" s="3">
+        <v>365</v>
+      </c>
+      <c r="M2" s="1">
+        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v>307</v>
+      </c>
+      <c r="N2" s="8">
+        <v>8</v>
+      </c>
+      <c r="O2" s="11">
+        <v>1.5</v>
+      </c>
+      <c r="P2" s="11">
+        <f>IFERROR(Table35[[#This Row],[Package Price
+($)]]/Table35[[#This Row],[Package Quantity]],"")</f>
+        <v>0.1875</v>
+      </c>
+      <c r="Q2" s="1">
+        <f>IFERROR(Table35[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table35[[#This Row],[Price per battery
+($)]],"")</f>
+        <v>1637.3333333333333</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="3">
+      <c r="C3" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="3">
         <v>1160</v>
       </c>
-      <c r="I2" s="3">
+      <c r="J3" s="3">
         <v>1080</v>
       </c>
-      <c r="J2" s="3">
+      <c r="K3" s="3">
         <v>1216</v>
       </c>
-      <c r="K2" s="3">
+      <c r="L3" s="3">
         <v>1136</v>
       </c>
-      <c r="L2" s="1">
-        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
+      <c r="M3" s="1">
+        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
         <v>1148</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="N3" s="8">
+        <v>4</v>
+      </c>
+      <c r="O3" s="11">
+        <v>17.09</v>
+      </c>
+      <c r="P3" s="11">
+        <f>IFERROR(Table35[[#This Row],[Package Price
+($)]]/Table35[[#This Row],[Package Quantity]],"")</f>
+        <v>4.2725</v>
+      </c>
+      <c r="Q3" s="1">
+        <f>IFERROR(Table35[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table35[[#This Row],[Price per battery
+($)]],"")</f>
+        <v>268.69514335868928</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="3">
-        <v>1476</v>
-      </c>
-      <c r="I3" s="3">
-        <v>1486</v>
-      </c>
-      <c r="J3" s="3">
-        <v>1382</v>
-      </c>
-      <c r="K3" s="3">
-        <v>1500</v>
-      </c>
-      <c r="L3" s="1">
-        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v>1461</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="C4" s="2" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="3">
-        <v>1542</v>
+        <v>5</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="I4" s="3">
-        <v>1465</v>
+        <v>1476</v>
       </c>
       <c r="J4" s="3">
-        <v>1474</v>
+        <v>1486</v>
       </c>
       <c r="K4" s="3">
-        <v>1561</v>
-      </c>
-      <c r="L4" s="1">
-        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v>1511</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+        <v>1382</v>
+      </c>
+      <c r="L4" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M4" s="1">
+        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v>1461</v>
+      </c>
+      <c r="N4" s="8">
+        <v>4</v>
+      </c>
+      <c r="O4" s="11">
+        <v>16.989999999999998</v>
+      </c>
+      <c r="P4" s="11">
+        <f>IFERROR(Table35[[#This Row],[Package Price
+($)]]/Table35[[#This Row],[Package Quantity]],"")</f>
+        <v>4.2474999999999996</v>
+      </c>
+      <c r="Q4" s="1">
+        <f>IFERROR(Table35[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table35[[#This Row],[Price per battery
+($)]],"")</f>
+        <v>343.96703943496175</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="3">
+        <v>1542</v>
+      </c>
+      <c r="J5" s="3">
+        <v>1465</v>
+      </c>
+      <c r="K5" s="3">
+        <v>1474</v>
+      </c>
+      <c r="L5" s="3">
+        <v>1561</v>
+      </c>
+      <c r="M5" s="1">
+        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v>1511</v>
+      </c>
+      <c r="N5" s="8">
+        <v>4</v>
+      </c>
+      <c r="O5" s="11">
+        <v>18.98</v>
+      </c>
+      <c r="P5" s="11">
+        <f>IFERROR(Table35[[#This Row],[Package Price
+($)]]/Table35[[#This Row],[Package Quantity]],"")</f>
+        <v>4.7450000000000001</v>
+      </c>
+      <c r="Q5" s="1">
+        <f>IFERROR(Table35[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table35[[#This Row],[Price per battery
+($)]],"")</f>
+        <v>318.44046364594311</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="3">
+      <c r="C6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="3">
         <v>1631</v>
       </c>
-      <c r="I5" s="3">
+      <c r="J6" s="3">
         <v>1692</v>
       </c>
-      <c r="J5" s="3">
+      <c r="K6" s="3">
         <v>1702</v>
       </c>
-      <c r="K5" s="3">
+      <c r="L6" s="3">
         <v>1716</v>
       </c>
-      <c r="L5" s="1">
-        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
+      <c r="M6" s="1">
+        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
         <v>1685</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="2" t="s">
+      <c r="N6" s="8">
+        <v>48</v>
+      </c>
+      <c r="O6" s="11">
+        <v>24.99</v>
+      </c>
+      <c r="P6" s="11">
+        <f>IFERROR(Table35[[#This Row],[Package Price
+($)]]/Table35[[#This Row],[Package Quantity]],"")</f>
+        <v>0.520625</v>
+      </c>
+      <c r="Q6" s="1">
+        <f>IFERROR(Table35[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table35[[#This Row],[Price per battery
+($)]],"")</f>
+        <v>3236.4945978391356</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" s="3">
-        <v>1816</v>
-      </c>
-      <c r="I6" s="3">
-        <v>1737</v>
-      </c>
-      <c r="J6" s="3">
-        <v>1771</v>
-      </c>
-      <c r="K6" s="3">
-        <v>1722</v>
-      </c>
-      <c r="L6" s="1">
-        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v>1762</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="C7" s="2" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="3">
+        <v>1816</v>
+      </c>
+      <c r="J7" s="3">
+        <v>1737</v>
+      </c>
+      <c r="K7" s="3">
+        <v>1771</v>
+      </c>
+      <c r="L7" s="3">
+        <v>1722</v>
+      </c>
+      <c r="M7" s="1">
+        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v>1762</v>
+      </c>
+      <c r="N7" s="8">
+        <v>4</v>
+      </c>
+      <c r="O7" s="11">
+        <v>24.99</v>
+      </c>
+      <c r="P7" s="11">
+        <f>IFERROR(Table35[[#This Row],[Package Price
+($)]]/Table35[[#This Row],[Package Quantity]],"")</f>
+        <v>6.2474999999999996</v>
+      </c>
+      <c r="Q7" s="1">
+        <f>IFERROR(Table35[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table35[[#This Row],[Price per battery
+($)]],"")</f>
+        <v>282.03281312525013</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" s="3">
+      <c r="C8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="3">
         <v>1821</v>
       </c>
-      <c r="I7" s="3">
+      <c r="J8" s="3">
         <v>1693</v>
       </c>
-      <c r="J7" s="3">
+      <c r="K8" s="3">
         <v>1853</v>
       </c>
-      <c r="K7" s="3">
+      <c r="L8" s="3">
         <v>1741</v>
       </c>
-      <c r="L7" s="1">
-        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
+      <c r="M8" s="1">
+        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
         <v>1777</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="1" t="str">
-        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N8" s="8">
+        <v>4</v>
+      </c>
+      <c r="O8" s="11">
+        <v>16.989999999999998</v>
+      </c>
+      <c r="P8" s="11">
+        <f>IFERROR(Table35[[#This Row],[Package Price
+($)]]/Table35[[#This Row],[Package Quantity]],"")</f>
+        <v>4.2474999999999996</v>
+      </c>
+      <c r="Q8" s="1">
+        <f>IFERROR(Table35[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table35[[#This Row],[Price per battery
+($)]],"")</f>
+        <v>418.36374337845797</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
-      <c r="H9" s="3"/>
+      <c r="H9" s="2"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
-      <c r="L9" s="1" t="str">
-        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L9" s="3"/>
+      <c r="M9" s="1" t="str">
+        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="P9" s="11" t="str">
+        <f>IFERROR(Table35[[#This Row],[Package Price
+($)]]/Table35[[#This Row],[Package Quantity]],"")</f>
+        <v/>
+      </c>
+      <c r="Q9" s="1" t="str">
+        <f>IFERROR(Table35[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table35[[#This Row],[Price per battery
+($)]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
-      <c r="H10" s="3"/>
+      <c r="H10" s="2"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
-      <c r="L10" s="1" t="str">
-        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L10" s="3"/>
+      <c r="M10" s="1" t="str">
+        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="P10" s="11" t="str">
+        <f>IFERROR(Table35[[#This Row],[Package Price
+($)]]/Table35[[#This Row],[Package Quantity]],"")</f>
+        <v/>
+      </c>
+      <c r="Q10" s="1" t="str">
+        <f>IFERROR(Table35[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table35[[#This Row],[Price per battery
+($)]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
-      <c r="H11" s="3"/>
+      <c r="H11" s="2"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-      <c r="L11" s="1" t="str">
-        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L11" s="3"/>
+      <c r="M11" s="1" t="str">
+        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="P11" s="11" t="str">
+        <f>IFERROR(Table35[[#This Row],[Package Price
+($)]]/Table35[[#This Row],[Package Quantity]],"")</f>
+        <v/>
+      </c>
+      <c r="Q11" s="1" t="str">
+        <f>IFERROR(Table35[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table35[[#This Row],[Price per battery
+($)]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="H12" s="3"/>
+      <c r="H12" s="2"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
-      <c r="L12" s="1" t="str">
-        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L12" s="3"/>
+      <c r="M12" s="1" t="str">
+        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="P12" s="11" t="str">
+        <f>IFERROR(Table35[[#This Row],[Package Price
+($)]]/Table35[[#This Row],[Package Quantity]],"")</f>
+        <v/>
+      </c>
+      <c r="Q12" s="1" t="str">
+        <f>IFERROR(Table35[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table35[[#This Row],[Price per battery
+($)]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
-      <c r="H13" s="3"/>
+      <c r="H13" s="2"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
-      <c r="L13" s="1" t="str">
-        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L13" s="3"/>
+      <c r="M13" s="1" t="str">
+        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="P13" s="11" t="str">
+        <f>IFERROR(Table35[[#This Row],[Package Price
+($)]]/Table35[[#This Row],[Package Quantity]],"")</f>
+        <v/>
+      </c>
+      <c r="Q13" s="1" t="str">
+        <f>IFERROR(Table35[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table35[[#This Row],[Price per battery
+($)]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
-      <c r="H14" s="3"/>
+      <c r="H14" s="2"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
-      <c r="L14" s="1" t="str">
-        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L14" s="3"/>
+      <c r="M14" s="1" t="str">
+        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="P14" s="11" t="str">
+        <f>IFERROR(Table35[[#This Row],[Package Price
+($)]]/Table35[[#This Row],[Package Quantity]],"")</f>
+        <v/>
+      </c>
+      <c r="Q14" s="1" t="str">
+        <f>IFERROR(Table35[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table35[[#This Row],[Price per battery
+($)]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
-      <c r="H15" s="3"/>
+      <c r="H15" s="2"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
-      <c r="L15" s="1" t="str">
-        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L15" s="3"/>
+      <c r="M15" s="1" t="str">
+        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="P15" s="11" t="str">
+        <f>IFERROR(Table35[[#This Row],[Package Price
+($)]]/Table35[[#This Row],[Package Quantity]],"")</f>
+        <v/>
+      </c>
+      <c r="Q15" s="1" t="str">
+        <f>IFERROR(Table35[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table35[[#This Row],[Price per battery
+($)]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-      <c r="H16" s="3"/>
+      <c r="H16" s="2"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-      <c r="L16" s="1" t="str">
-        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L16" s="3"/>
+      <c r="M16" s="1" t="str">
+        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="P16" s="11" t="str">
+        <f>IFERROR(Table35[[#This Row],[Package Price
+($)]]/Table35[[#This Row],[Package Quantity]],"")</f>
+        <v/>
+      </c>
+      <c r="Q16" s="1" t="str">
+        <f>IFERROR(Table35[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table35[[#This Row],[Price per battery
+($)]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
-      <c r="H17" s="3"/>
+      <c r="H17" s="2"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
-      <c r="L17" s="1" t="str">
-        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L17" s="3"/>
+      <c r="M17" s="1" t="str">
+        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="P17" s="11" t="str">
+        <f>IFERROR(Table35[[#This Row],[Package Price
+($)]]/Table35[[#This Row],[Package Quantity]],"")</f>
+        <v/>
+      </c>
+      <c r="Q17" s="1" t="str">
+        <f>IFERROR(Table35[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table35[[#This Row],[Price per battery
+($)]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
-      <c r="H18" s="3"/>
+      <c r="H18" s="2"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
-      <c r="L18" s="1" t="str">
-        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L18" s="3"/>
+      <c r="M18" s="1" t="str">
+        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="P18" s="11" t="str">
+        <f>IFERROR(Table35[[#This Row],[Package Price
+($)]]/Table35[[#This Row],[Package Quantity]],"")</f>
+        <v/>
+      </c>
+      <c r="Q18" s="1" t="str">
+        <f>IFERROR(Table35[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table35[[#This Row],[Price per battery
+($)]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
-      <c r="H19" s="3"/>
+      <c r="H19" s="2"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-      <c r="L19" s="1" t="str">
-        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L19" s="3"/>
+      <c r="M19" s="1" t="str">
+        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="P19" s="11" t="str">
+        <f>IFERROR(Table35[[#This Row],[Package Price
+($)]]/Table35[[#This Row],[Package Quantity]],"")</f>
+        <v/>
+      </c>
+      <c r="Q19" s="1" t="str">
+        <f>IFERROR(Table35[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table35[[#This Row],[Price per battery
+($)]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
-      <c r="H20" s="3"/>
+      <c r="H20" s="2"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
-      <c r="L20" s="1" t="str">
-        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L20" s="3"/>
+      <c r="M20" s="1" t="str">
+        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="P20" s="11" t="str">
+        <f>IFERROR(Table35[[#This Row],[Package Price
+($)]]/Table35[[#This Row],[Package Quantity]],"")</f>
+        <v/>
+      </c>
+      <c r="Q20" s="1" t="str">
+        <f>IFERROR(Table35[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table35[[#This Row],[Price per battery
+($)]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
-      <c r="H21" s="3"/>
+      <c r="H21" s="2"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
-      <c r="L21" s="1" t="str">
-        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L21" s="3"/>
+      <c r="M21" s="1" t="str">
+        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="P21" s="11" t="str">
+        <f>IFERROR(Table35[[#This Row],[Package Price
+($)]]/Table35[[#This Row],[Package Quantity]],"")</f>
+        <v/>
+      </c>
+      <c r="Q21" s="1" t="str">
+        <f>IFERROR(Table35[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table35[[#This Row],[Price per battery
+($)]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
-      <c r="H22" s="3"/>
+      <c r="H22" s="2"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
-      <c r="L22" s="1" t="str">
-        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L22" s="3"/>
+      <c r="M22" s="1" t="str">
+        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="P22" s="11" t="str">
+        <f>IFERROR(Table35[[#This Row],[Package Price
+($)]]/Table35[[#This Row],[Package Quantity]],"")</f>
+        <v/>
+      </c>
+      <c r="Q22" s="1" t="str">
+        <f>IFERROR(Table35[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table35[[#This Row],[Price per battery
+($)]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
-      <c r="H23" s="3"/>
+      <c r="H23" s="2"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
-      <c r="L23" s="1" t="str">
-        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L23" s="3"/>
+      <c r="M23" s="1" t="str">
+        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="P23" s="11" t="str">
+        <f>IFERROR(Table35[[#This Row],[Package Price
+($)]]/Table35[[#This Row],[Package Quantity]],"")</f>
+        <v/>
+      </c>
+      <c r="Q23" s="1" t="str">
+        <f>IFERROR(Table35[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table35[[#This Row],[Price per battery
+($)]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
-      <c r="H24" s="3"/>
+      <c r="H24" s="2"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
-      <c r="L24" s="1" t="str">
-        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L24" s="3"/>
+      <c r="M24" s="1" t="str">
+        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="P24" s="11" t="str">
+        <f>IFERROR(Table35[[#This Row],[Package Price
+($)]]/Table35[[#This Row],[Package Quantity]],"")</f>
+        <v/>
+      </c>
+      <c r="Q24" s="1" t="str">
+        <f>IFERROR(Table35[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table35[[#This Row],[Price per battery
+($)]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
-      <c r="H25" s="3"/>
+      <c r="H25" s="2"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
-      <c r="L25" s="1" t="str">
-        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
+      <c r="L25" s="3"/>
+      <c r="M25" s="1" t="str">
+        <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="P25" s="11" t="str">
+        <f>IFERROR(Table35[[#This Row],[Package Price
+($)]]/Table35[[#This Row],[Package Quantity]],"")</f>
+        <v/>
+      </c>
+      <c r="Q25" s="1" t="str">
+        <f>IFERROR(Table35[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table35[[#This Row],[Price per battery
+($)]],"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="L2:L25">
+  <conditionalFormatting sqref="M2:M25">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -1345,667 +1884,1095 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EABD02D-1588-4CBA-A3C2-B7A49904AF92}">
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.85546875" customWidth="1"/>
-    <col min="4" max="4" width="7.5703125" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.85546875" customWidth="1"/>
+    <col min="5" max="5" width="7.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11" style="8" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>27</v>
+        <v>43</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="P1" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q1" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="3">
+        <v>127</v>
+      </c>
+      <c r="J2" s="3">
+        <v>151</v>
+      </c>
+      <c r="K2" s="3">
+        <v>131</v>
+      </c>
+      <c r="L2" s="3">
+        <v>125</v>
+      </c>
+      <c r="M2" s="1">
+        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v>134</v>
+      </c>
+      <c r="N2" s="8">
         <v>8</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="3">
-        <v>379</v>
-      </c>
-      <c r="I2" s="3">
-        <v>334</v>
-      </c>
-      <c r="J2" s="3">
-        <v>403</v>
-      </c>
-      <c r="K2" s="3">
-        <v>348</v>
-      </c>
-      <c r="L2" s="1">
-        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v>366</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="O2" s="11">
+        <v>1.5</v>
+      </c>
+      <c r="P2" s="11">
+        <f>IFERROR(Table3[[#This Row],[Package Price
+($)]]/Table3[[#This Row],[Package Quantity]],"")</f>
+        <v>0.1875</v>
+      </c>
+      <c r="Q2" s="1">
+        <f>IFERROR(Table3[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table3[[#This Row],[Price per battery
+($)]],"")</f>
+        <v>714.66666666666663</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="3">
-        <v>377</v>
+        <v>5</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="I3" s="3">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="J3" s="3">
-        <v>372</v>
+        <v>334</v>
       </c>
       <c r="K3" s="3">
-        <v>378</v>
-      </c>
-      <c r="L3" s="1">
-        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v>378</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+        <v>403</v>
+      </c>
+      <c r="L3" s="3">
+        <v>348</v>
+      </c>
+      <c r="M3" s="1">
+        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v>366</v>
+      </c>
+      <c r="N3" s="8">
+        <v>4</v>
+      </c>
+      <c r="O3" s="11">
+        <v>16.98</v>
+      </c>
+      <c r="P3" s="11">
+        <f>IFERROR(Table3[[#This Row],[Package Price
+($)]]/Table3[[#This Row],[Package Quantity]],"")</f>
+        <v>4.2450000000000001</v>
+      </c>
+      <c r="Q3" s="1">
+        <f>IFERROR(Table3[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table3[[#This Row],[Price per battery
+($)]],"")</f>
+        <v>86.219081272084807</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="3">
+        <v>377</v>
+      </c>
+      <c r="J4" s="3">
+        <v>384</v>
+      </c>
+      <c r="K4" s="3">
+        <v>372</v>
+      </c>
+      <c r="L4" s="3">
+        <v>378</v>
+      </c>
+      <c r="M4" s="1">
+        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v>378</v>
+      </c>
+      <c r="N4" s="8">
+        <v>4</v>
+      </c>
+      <c r="O4" s="11">
+        <v>16.989999999999998</v>
+      </c>
+      <c r="P4" s="11">
+        <f>IFERROR(Table3[[#This Row],[Package Price
+($)]]/Table3[[#This Row],[Package Quantity]],"")</f>
+        <v>4.2474999999999996</v>
+      </c>
+      <c r="Q4" s="1">
+        <f>IFERROR(Table3[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table3[[#This Row],[Price per battery
+($)]],"")</f>
+        <v>88.993525603296064</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="3">
+        <v>347</v>
+      </c>
+      <c r="J5" s="3">
+        <v>485</v>
+      </c>
+      <c r="K5" s="3">
+        <v>485</v>
+      </c>
+      <c r="L5" s="3">
+        <v>464</v>
+      </c>
+      <c r="M5" s="1">
+        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v>445</v>
+      </c>
+      <c r="N5" s="8">
+        <v>4</v>
+      </c>
+      <c r="O5" s="11">
+        <v>15.99</v>
+      </c>
+      <c r="P5" s="11">
+        <f>IFERROR(Table3[[#This Row],[Package Price
+($)]]/Table3[[#This Row],[Package Quantity]],"")</f>
+        <v>3.9975000000000001</v>
+      </c>
+      <c r="Q5" s="1">
+        <f>IFERROR(Table3[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table3[[#This Row],[Price per battery
+($)]],"")</f>
+        <v>111.31957473420889</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="3">
+        <v>502</v>
+      </c>
+      <c r="J6" s="3">
+        <v>475</v>
+      </c>
+      <c r="K6" s="3">
+        <v>468</v>
+      </c>
+      <c r="L6" s="3">
+        <v>496</v>
+      </c>
+      <c r="M6" s="1">
+        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v>485</v>
+      </c>
+      <c r="N6" s="8">
+        <v>48</v>
+      </c>
+      <c r="O6" s="11">
+        <v>21.93</v>
+      </c>
+      <c r="P6" s="11">
+        <f>IFERROR(Table3[[#This Row],[Package Price
+($)]]/Table3[[#This Row],[Package Quantity]],"")</f>
+        <v>0.45687499999999998</v>
+      </c>
+      <c r="Q6" s="1">
+        <f>IFERROR(Table3[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table3[[#This Row],[Price per battery
+($)]],"")</f>
+        <v>1061.5595075239398</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="3">
-        <v>347</v>
-      </c>
-      <c r="I4" s="3">
-        <v>485</v>
-      </c>
-      <c r="J4" s="3">
-        <v>485</v>
-      </c>
-      <c r="K4" s="3">
-        <v>464</v>
-      </c>
-      <c r="L4" s="1">
-        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v>445</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="3">
-        <v>502</v>
-      </c>
-      <c r="I5" s="3">
-        <v>475</v>
-      </c>
-      <c r="J5" s="3">
-        <v>468</v>
-      </c>
-      <c r="K5" s="3">
-        <v>496</v>
-      </c>
-      <c r="L5" s="1">
-        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v>485</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" s="3">
-        <v>596</v>
-      </c>
-      <c r="I6" s="3">
-        <v>593</v>
-      </c>
-      <c r="J6" s="3">
-        <v>547</v>
-      </c>
-      <c r="K6" s="3">
-        <v>574</v>
-      </c>
-      <c r="L6" s="1">
-        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v>578</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="G7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" s="3">
-        <v>605</v>
+        <v>5</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="I7" s="3">
         <v>596</v>
       </c>
       <c r="J7" s="3">
+        <v>593</v>
+      </c>
+      <c r="K7" s="3">
+        <v>547</v>
+      </c>
+      <c r="L7" s="3">
+        <v>574</v>
+      </c>
+      <c r="M7" s="1">
+        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v>578</v>
+      </c>
+      <c r="N7" s="8">
+        <v>4</v>
+      </c>
+      <c r="O7" s="11">
+        <v>16.989999999999998</v>
+      </c>
+      <c r="P7" s="11">
+        <f>IFERROR(Table3[[#This Row],[Package Price
+($)]]/Table3[[#This Row],[Package Quantity]],"")</f>
+        <v>4.2474999999999996</v>
+      </c>
+      <c r="Q7" s="1">
+        <f>IFERROR(Table3[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table3[[#This Row],[Price per battery
+($)]],"")</f>
+        <v>136.08004708652149</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="3">
+        <v>605</v>
+      </c>
+      <c r="J8" s="3">
+        <v>596</v>
+      </c>
+      <c r="K8" s="3">
         <v>620</v>
       </c>
-      <c r="K7" s="3">
+      <c r="L8" s="3">
         <v>576</v>
       </c>
-      <c r="L7" s="1">
-        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
+      <c r="M8" s="1">
+        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
         <v>599</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="N8" s="8">
         <v>16</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="O8" s="11">
+        <v>9.7899999999999991</v>
+      </c>
+      <c r="P8" s="11">
+        <f>IFERROR(Table3[[#This Row],[Package Price
+($)]]/Table3[[#This Row],[Package Quantity]],"")</f>
+        <v>0.61187499999999995</v>
+      </c>
+      <c r="Q8" s="1">
+        <f>IFERROR(Table3[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table3[[#This Row],[Price per battery
+($)]],"")</f>
+        <v>978.95812053115435</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G8" s="2" t="s">
+      <c r="E9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="3">
+      <c r="G9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="3">
         <v>635</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J9" s="3">
         <v>635</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K9" s="3">
         <v>636</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L9" s="3">
         <v>652</v>
       </c>
-      <c r="L8" s="1">
-        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
+      <c r="M9" s="1">
+        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
         <v>640</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="1" t="str">
-        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N9" s="8">
+        <v>4</v>
+      </c>
+      <c r="O9" s="11">
+        <v>21.99</v>
+      </c>
+      <c r="P9" s="11">
+        <f>IFERROR(Table3[[#This Row],[Package Price
+($)]]/Table3[[#This Row],[Package Quantity]],"")</f>
+        <v>5.4974999999999996</v>
+      </c>
+      <c r="Q9" s="1">
+        <f>IFERROR(Table3[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table3[[#This Row],[Price per battery
+($)]],"")</f>
+        <v>116.41655297862665</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
-      <c r="H10" s="3"/>
+      <c r="H10" s="2"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
-      <c r="L10" s="1" t="str">
-        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L10" s="3"/>
+      <c r="M10" s="1" t="str">
+        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="P10" s="11" t="str">
+        <f>IFERROR(Table3[[#This Row],[Package Price
+($)]]/Table3[[#This Row],[Package Quantity]],"")</f>
+        <v/>
+      </c>
+      <c r="Q10" s="1" t="str">
+        <f>IFERROR(Table3[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table3[[#This Row],[Price per battery
+($)]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
-      <c r="H11" s="3"/>
+      <c r="H11" s="2"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-      <c r="L11" s="1" t="str">
-        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L11" s="3"/>
+      <c r="M11" s="1" t="str">
+        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="P11" s="11" t="str">
+        <f>IFERROR(Table3[[#This Row],[Package Price
+($)]]/Table3[[#This Row],[Package Quantity]],"")</f>
+        <v/>
+      </c>
+      <c r="Q11" s="1" t="str">
+        <f>IFERROR(Table3[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table3[[#This Row],[Price per battery
+($)]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="H12" s="3"/>
+      <c r="H12" s="2"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
-      <c r="L12" s="1" t="str">
-        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L12" s="3"/>
+      <c r="M12" s="1" t="str">
+        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="P12" s="11" t="str">
+        <f>IFERROR(Table3[[#This Row],[Package Price
+($)]]/Table3[[#This Row],[Package Quantity]],"")</f>
+        <v/>
+      </c>
+      <c r="Q12" s="1" t="str">
+        <f>IFERROR(Table3[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table3[[#This Row],[Price per battery
+($)]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
-      <c r="H13" s="3"/>
+      <c r="H13" s="2"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
-      <c r="L13" s="1" t="str">
-        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L13" s="3"/>
+      <c r="M13" s="1" t="str">
+        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="P13" s="11" t="str">
+        <f>IFERROR(Table3[[#This Row],[Package Price
+($)]]/Table3[[#This Row],[Package Quantity]],"")</f>
+        <v/>
+      </c>
+      <c r="Q13" s="1" t="str">
+        <f>IFERROR(Table3[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table3[[#This Row],[Price per battery
+($)]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
-      <c r="H14" s="3"/>
+      <c r="H14" s="2"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
-      <c r="L14" s="1" t="str">
-        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L14" s="3"/>
+      <c r="M14" s="1" t="str">
+        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="P14" s="11" t="str">
+        <f>IFERROR(Table3[[#This Row],[Package Price
+($)]]/Table3[[#This Row],[Package Quantity]],"")</f>
+        <v/>
+      </c>
+      <c r="Q14" s="1" t="str">
+        <f>IFERROR(Table3[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table3[[#This Row],[Price per battery
+($)]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
-      <c r="H15" s="3"/>
+      <c r="H15" s="2"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
-      <c r="L15" s="1" t="str">
-        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L15" s="3"/>
+      <c r="M15" s="1" t="str">
+        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="P15" s="11" t="str">
+        <f>IFERROR(Table3[[#This Row],[Package Price
+($)]]/Table3[[#This Row],[Package Quantity]],"")</f>
+        <v/>
+      </c>
+      <c r="Q15" s="1" t="str">
+        <f>IFERROR(Table3[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table3[[#This Row],[Price per battery
+($)]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-      <c r="H16" s="3"/>
+      <c r="H16" s="2"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-      <c r="L16" s="1" t="str">
-        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L16" s="3"/>
+      <c r="M16" s="1" t="str">
+        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="P16" s="11" t="str">
+        <f>IFERROR(Table3[[#This Row],[Package Price
+($)]]/Table3[[#This Row],[Package Quantity]],"")</f>
+        <v/>
+      </c>
+      <c r="Q16" s="1" t="str">
+        <f>IFERROR(Table3[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table3[[#This Row],[Price per battery
+($)]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
-      <c r="H17" s="3"/>
+      <c r="H17" s="2"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
-      <c r="L17" s="1" t="str">
-        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L17" s="3"/>
+      <c r="M17" s="1" t="str">
+        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="P17" s="11" t="str">
+        <f>IFERROR(Table3[[#This Row],[Package Price
+($)]]/Table3[[#This Row],[Package Quantity]],"")</f>
+        <v/>
+      </c>
+      <c r="Q17" s="1" t="str">
+        <f>IFERROR(Table3[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table3[[#This Row],[Price per battery
+($)]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
-      <c r="H18" s="3"/>
+      <c r="H18" s="2"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
-      <c r="L18" s="1" t="str">
-        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L18" s="3"/>
+      <c r="M18" s="1" t="str">
+        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="P18" s="11" t="str">
+        <f>IFERROR(Table3[[#This Row],[Package Price
+($)]]/Table3[[#This Row],[Package Quantity]],"")</f>
+        <v/>
+      </c>
+      <c r="Q18" s="1" t="str">
+        <f>IFERROR(Table3[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table3[[#This Row],[Price per battery
+($)]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
-      <c r="H19" s="3"/>
+      <c r="H19" s="2"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-      <c r="L19" s="1" t="str">
-        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L19" s="3"/>
+      <c r="M19" s="1" t="str">
+        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="P19" s="11" t="str">
+        <f>IFERROR(Table3[[#This Row],[Package Price
+($)]]/Table3[[#This Row],[Package Quantity]],"")</f>
+        <v/>
+      </c>
+      <c r="Q19" s="1" t="str">
+        <f>IFERROR(Table3[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table3[[#This Row],[Price per battery
+($)]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
-      <c r="H20" s="3"/>
+      <c r="H20" s="2"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
-      <c r="L20" s="1" t="str">
-        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L20" s="3"/>
+      <c r="M20" s="1" t="str">
+        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="P20" s="11" t="str">
+        <f>IFERROR(Table3[[#This Row],[Package Price
+($)]]/Table3[[#This Row],[Package Quantity]],"")</f>
+        <v/>
+      </c>
+      <c r="Q20" s="1" t="str">
+        <f>IFERROR(Table3[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table3[[#This Row],[Price per battery
+($)]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
-      <c r="H21" s="3"/>
+      <c r="H21" s="2"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
-      <c r="L21" s="1" t="str">
-        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L21" s="3"/>
+      <c r="M21" s="1" t="str">
+        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="P21" s="11" t="str">
+        <f>IFERROR(Table3[[#This Row],[Package Price
+($)]]/Table3[[#This Row],[Package Quantity]],"")</f>
+        <v/>
+      </c>
+      <c r="Q21" s="1" t="str">
+        <f>IFERROR(Table3[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table3[[#This Row],[Price per battery
+($)]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
-      <c r="H22" s="3"/>
+      <c r="H22" s="2"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
-      <c r="L22" s="1" t="str">
-        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L22" s="3"/>
+      <c r="M22" s="1" t="str">
+        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="P22" s="11" t="str">
+        <f>IFERROR(Table3[[#This Row],[Package Price
+($)]]/Table3[[#This Row],[Package Quantity]],"")</f>
+        <v/>
+      </c>
+      <c r="Q22" s="1" t="str">
+        <f>IFERROR(Table3[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table3[[#This Row],[Price per battery
+($)]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
-      <c r="H23" s="3"/>
+      <c r="H23" s="2"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
-      <c r="L23" s="1" t="str">
-        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L23" s="3"/>
+      <c r="M23" s="1" t="str">
+        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="P23" s="11" t="str">
+        <f>IFERROR(Table3[[#This Row],[Package Price
+($)]]/Table3[[#This Row],[Package Quantity]],"")</f>
+        <v/>
+      </c>
+      <c r="Q23" s="1" t="str">
+        <f>IFERROR(Table3[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table3[[#This Row],[Price per battery
+($)]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
-      <c r="H24" s="3"/>
+      <c r="H24" s="2"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
-      <c r="L24" s="1" t="str">
-        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L24" s="3"/>
+      <c r="M24" s="1" t="str">
+        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="P24" s="11" t="str">
+        <f>IFERROR(Table3[[#This Row],[Package Price
+($)]]/Table3[[#This Row],[Package Quantity]],"")</f>
+        <v/>
+      </c>
+      <c r="Q24" s="1" t="str">
+        <f>IFERROR(Table3[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table3[[#This Row],[Price per battery
+($)]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
-      <c r="H25" s="3"/>
+      <c r="H25" s="2"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
-      <c r="L25" s="1" t="str">
-        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (Test '#1)]:[Capacity (Test '#4)]]),0),"")</f>
+      <c r="L25" s="3"/>
+      <c r="M25" s="1" t="str">
+        <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (mAh)
+(Test '#1)]:[Capacity (mAh)
+(Test '#4)]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="P25" s="11" t="str">
+        <f>IFERROR(Table3[[#This Row],[Package Price
+($)]]/Table3[[#This Row],[Package Quantity]],"")</f>
+        <v/>
+      </c>
+      <c r="Q25" s="1" t="str">
+        <f>IFERROR(Table3[[#This Row],[Capacity (mAh)
+(Averaged)]]/Table3[[#This Row],[Price per battery
+($)]],"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="L2:L25">
+  <conditionalFormatting sqref="M2:M25">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -2036,42 +3003,42 @@
   <sheetData>
     <row r="1" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/hardware/battery-capacity-tests_lithium-ion_AA-AAA.xlsx
+++ b/hardware/battery-capacity-tests_lithium-ion_AA-AAA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcava\Documents\GitHub\Coding\hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E60155C7-F328-4CB7-AF0B-0381D9B7B9DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF976881-59EB-433E-8707-82E05B752F54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{E5D7BF72-F0C5-4096-89C0-8DC37475FB76}"/>
+    <workbookView xWindow="645" yWindow="780" windowWidth="24555" windowHeight="19290" xr2:uid="{E5D7BF72-F0C5-4096-89C0-8DC37475FB76}"/>
   </bookViews>
   <sheets>
     <sheet name="AA Batteries" sheetId="4" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="51">
   <si>
     <t>EBL</t>
   </si>
@@ -194,6 +194,12 @@
   </si>
   <si>
     <t>Lithium Ion</t>
+  </si>
+  <si>
+    <t>ALLMAX</t>
+  </si>
+  <si>
+    <t>Lithium</t>
   </si>
 </sst>
 </file>
@@ -347,18 +353,6 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="dotted">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="164" formatCode="0&quot; mAh&quot;"/>
     </dxf>
     <dxf>
@@ -384,6 +378,18 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="0&quot; mAh&quot;"/>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="dotted">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
@@ -434,28 +440,28 @@
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{CBABFE4A-DB4B-478A-A196-6B10725888CE}" name="Battery Brand" dataDxfId="22"/>
     <tableColumn id="2" xr3:uid="{A4C15DEC-98CA-4B4A-AA6D-9D8629196B6D}" name="Form Factor"/>
-    <tableColumn id="18" xr3:uid="{5C2654CB-3147-4CBC-B035-883A9090E4E6}" name="Chemistry" dataDxfId="12"/>
+    <tableColumn id="18" xr3:uid="{5C2654CB-3147-4CBC-B035-883A9090E4E6}" name="Chemistry" dataDxfId="21"/>
     <tableColumn id="3" xr3:uid="{C5D6165E-2DC1-490A-8745-775A230CE959}" name="Plug Loc"/>
     <tableColumn id="4" xr3:uid="{76E5C7FE-A9FC-4892-AA2F-F4BDBC0FE43E}" name="USB Type"/>
     <tableColumn id="5" xr3:uid="{0B30B98B-6A8B-4BC5-AAA4-52D69388E8A1}" name="Splitter Incl."/>
     <tableColumn id="6" xr3:uid="{679FA49F-E3B8-466B-A769-C279FED07A47}" name="Cutoff_x000a_(V)"/>
     <tableColumn id="7" xr3:uid="{0749C5D5-9FE3-4320-A646-E78C6602DB2D}" name="Current_x000a_(A)"/>
-    <tableColumn id="8" xr3:uid="{FC5DC19F-46DB-49F0-B6EB-F8D8DFCC5119}" name="Capacity (mAh)_x000a_(Test #1)" dataDxfId="21"/>
-    <tableColumn id="9" xr3:uid="{2C2758A8-2AF5-47E7-BF85-99A3D8B3BA30}" name="Capacity (mAh)_x000a_(Test #2)" dataDxfId="20"/>
-    <tableColumn id="10" xr3:uid="{33DF939F-2A16-4823-AACA-AC4D2782FCC1}" name="Capacity (mAh)_x000a_(Test #3)" dataDxfId="19"/>
-    <tableColumn id="11" xr3:uid="{DD1EEECD-4600-48C0-A802-DB79834A7A50}" name="Capacity (mAh)_x000a_(Test #4)" dataDxfId="18"/>
-    <tableColumn id="12" xr3:uid="{815B7A98-D189-4530-8370-36E96E9386A8}" name="Capacity (mAh)_x000a_(Averaged)" dataDxfId="17">
+    <tableColumn id="8" xr3:uid="{FC5DC19F-46DB-49F0-B6EB-F8D8DFCC5119}" name="Capacity (mAh)_x000a_(Test #1)" dataDxfId="20"/>
+    <tableColumn id="9" xr3:uid="{2C2758A8-2AF5-47E7-BF85-99A3D8B3BA30}" name="Capacity (mAh)_x000a_(Test #2)" dataDxfId="19"/>
+    <tableColumn id="10" xr3:uid="{33DF939F-2A16-4823-AACA-AC4D2782FCC1}" name="Capacity (mAh)_x000a_(Test #3)" dataDxfId="18"/>
+    <tableColumn id="11" xr3:uid="{DD1EEECD-4600-48C0-A802-DB79834A7A50}" name="Capacity (mAh)_x000a_(Test #4)" dataDxfId="17"/>
+    <tableColumn id="12" xr3:uid="{815B7A98-D189-4530-8370-36E96E9386A8}" name="Capacity (mAh)_x000a_(Averaged)" dataDxfId="16">
       <calculatedColumnFormula>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (mAh)
 (Test '#1)]:[Capacity (mAh)
 (Test '#4)]]),0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{FB50ABF7-3A80-4E6B-B421-533E61A624AE}" name="Package Quantity" dataDxfId="16"/>
-    <tableColumn id="14" xr3:uid="{BAAC862F-FE09-469C-B505-5B1D17C687E4}" name="Package Price_x000a_($)" dataDxfId="15"/>
-    <tableColumn id="15" xr3:uid="{4DAA5FFD-D836-4119-968C-53A1BFEA75AC}" name="Price per battery_x000a_($)" dataDxfId="14">
+    <tableColumn id="13" xr3:uid="{FB50ABF7-3A80-4E6B-B421-533E61A624AE}" name="Package Quantity" dataDxfId="15"/>
+    <tableColumn id="14" xr3:uid="{BAAC862F-FE09-469C-B505-5B1D17C687E4}" name="Package Price_x000a_($)" dataDxfId="14"/>
+    <tableColumn id="15" xr3:uid="{4DAA5FFD-D836-4119-968C-53A1BFEA75AC}" name="Price per battery_x000a_($)" dataDxfId="13">
       <calculatedColumnFormula>IFERROR(Table35[[#This Row],[Package Price
 ($)]]/Table35[[#This Row],[Package Quantity]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{B90ADC68-DA10-4B4A-816B-714216F488CF}" name="Capacity per Dollar (mAh)" dataDxfId="13">
+    <tableColumn id="16" xr3:uid="{B90ADC68-DA10-4B4A-816B-714216F488CF}" name="Capacity per Dollar (mAh)" dataDxfId="12">
       <calculatedColumnFormula>IFERROR(Table35[[#This Row],[Capacity (mAh)
 (Averaged)]]/Table35[[#This Row],[Price per battery
 ($)]],"")</calculatedColumnFormula>
@@ -1301,36 +1307,64 @@
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
+      <c r="A9" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="B9" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="1" t="str">
+      <c r="C9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="3">
+        <v>3236</v>
+      </c>
+      <c r="J9" s="3">
+        <v>3236</v>
+      </c>
+      <c r="K9" s="3">
+        <v>3158</v>
+      </c>
+      <c r="L9" s="3">
+        <v>3170</v>
+      </c>
+      <c r="M9" s="1">
         <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (mAh)
 (Test '#1)]:[Capacity (mAh)
 (Test '#4)]]),0),"")</f>
-        <v/>
-      </c>
-      <c r="P9" s="11" t="str">
+        <v>3200</v>
+      </c>
+      <c r="N9" s="8">
+        <v>24</v>
+      </c>
+      <c r="O9" s="11">
+        <v>26.99</v>
+      </c>
+      <c r="P9" s="11">
         <f>IFERROR(Table35[[#This Row],[Package Price
 ($)]]/Table35[[#This Row],[Package Quantity]],"")</f>
-        <v/>
-      </c>
-      <c r="Q9" s="1" t="str">
+        <v>1.1245833333333333</v>
+      </c>
+      <c r="Q9" s="1">
         <f>IFERROR(Table35[[#This Row],[Capacity (mAh)
 (Averaged)]]/Table35[[#This Row],[Price per battery
 ($)]],"")</f>
-        <v/>
+        <v>2845.4983327158207</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -2444,36 +2478,64 @@
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
+      <c r="A10" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="B10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="1" t="str">
+        <v>6</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1201</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1227</v>
+      </c>
+      <c r="K10" s="3">
+        <v>1201</v>
+      </c>
+      <c r="L10" s="3">
+        <v>1209</v>
+      </c>
+      <c r="M10" s="1">
         <f>IFERROR(ROUND(AVERAGE(Table3[[#This Row],[Capacity (mAh)
 (Test '#1)]:[Capacity (mAh)
 (Test '#4)]]),0),"")</f>
-        <v/>
-      </c>
-      <c r="P10" s="11" t="str">
+        <v>1210</v>
+      </c>
+      <c r="N10" s="8">
+        <v>24</v>
+      </c>
+      <c r="O10" s="11">
+        <v>24.99</v>
+      </c>
+      <c r="P10" s="11">
         <f>IFERROR(Table3[[#This Row],[Package Price
 ($)]]/Table3[[#This Row],[Package Quantity]],"")</f>
-        <v/>
-      </c>
-      <c r="Q10" s="1" t="str">
+        <v>1.04125</v>
+      </c>
+      <c r="Q10" s="1">
         <f>IFERROR(Table3[[#This Row],[Capacity (mAh)
 (Averaged)]]/Table3[[#This Row],[Price per battery
 ($)]],"")</f>
-        <v/>
+        <v>1162.0648259303721</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">

--- a/hardware/battery-capacity-tests_lithium-ion_AA-AAA.xlsx
+++ b/hardware/battery-capacity-tests_lithium-ion_AA-AAA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcava\Documents\GitHub\Coding\hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93BC8CBD-FFBB-498B-AA68-9E0722722326}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37644B9F-22A9-4716-B303-DF7DAC017697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="38700" windowHeight="15345" xr2:uid="{E5D7BF72-F0C5-4096-89C0-8DC37475FB76}"/>
+    <workbookView xWindow="3900" yWindow="3900" windowWidth="38700" windowHeight="15345" xr2:uid="{E5D7BF72-F0C5-4096-89C0-8DC37475FB76}"/>
   </bookViews>
   <sheets>
     <sheet name="AA Batteries" sheetId="4" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="55">
   <si>
     <t>EBL</t>
   </si>
@@ -134,9 +134,6 @@
   </si>
   <si>
     <t>6. Press "OK" to confirm the cutoff voltage and the HW-586 will run until the battery reaches 0.8V</t>
-  </si>
-  <si>
-    <t>e-CIRCUIT</t>
   </si>
   <si>
     <t>7. Once test is complete, the HW-586 will bleak rapidly, displaying the "Ah" (Amp-hours) result - Save this into desired spreadsheet or other record keeping location</t>
@@ -212,6 +209,12 @@
   <si>
     <t>Capacity (Claimed)
 (mAh)</t>
+  </si>
+  <si>
+    <t>ENERGIZER ULTIMATE</t>
+  </si>
+  <si>
+    <t>E-CIRCUIT</t>
   </si>
 </sst>
 </file>
@@ -965,7 +968,7 @@
   <dimension ref="A1:T25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.42578125" style="7" customWidth="1"/>
     <col min="2" max="2" width="9.140625" style="7"/>
     <col min="3" max="3" width="12.28515625" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.140625" style="16" bestFit="1" customWidth="1"/>
@@ -993,13 +996,13 @@
         <v>24</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>8</v>
@@ -1011,51 +1014,51 @@
         <v>15</v>
       </c>
       <c r="I1" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J1" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q1" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="R1" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="S1" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="T1" s="8" t="s">
         <v>42</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="M1" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="O1" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="P1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q1" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="R1" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="S1" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="T1" s="8" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>19</v>
@@ -1129,7 +1132,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D3" s="4">
         <v>3300</v>
@@ -1201,7 +1204,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D4" s="4">
         <v>2600</v>
@@ -1275,7 +1278,7 @@
         <v>5</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D5" s="4">
         <v>2600</v>
@@ -1349,7 +1352,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D6" s="4">
         <v>4612</v>
@@ -1423,7 +1426,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D7" s="4">
         <v>2960</v>
@@ -1497,7 +1500,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D8" s="4">
         <v>3300</v>
@@ -1571,7 +1574,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D9" s="4">
         <v>3500</v>
@@ -1639,13 +1642,13 @@
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D10" s="4">
         <v>4800</v>
@@ -1712,45 +1715,77 @@
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" s="6"/>
+      <c r="A11" s="6" t="s">
+        <v>53</v>
+      </c>
       <c r="B11" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="3" t="str">
+      <c r="C11" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="4">
+        <v>4500</v>
+      </c>
+      <c r="E11" s="12">
+        <v>1</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="K11" s="13">
+        <v>3318</v>
+      </c>
+      <c r="L11" s="13">
+        <v>3441</v>
+      </c>
+      <c r="M11" s="13">
+        <v>3493</v>
+      </c>
+      <c r="N11" s="13">
+        <v>3511</v>
+      </c>
+      <c r="O11" s="3">
         <f>IFERROR(ROUND(AVERAGE(Table35[[#This Row],[Capacity (mAh)
 (Test '#1)]:[Capacity (mAh)
 (Test '#4)]]),0),"")</f>
-        <v/>
-      </c>
-      <c r="P11" s="3" t="str">
+        <v>3441</v>
+      </c>
+      <c r="P11" s="3">
         <f>IF(OR(ISBLANK(Table35[[#This Row],[Capacity (Claimed)
 (mWh)]]),(Table35[[#This Row],[Capacity (Claimed)
 (mWh)]]="-")),"-",(Table35[[#This Row],[Capacity (Claimed)
 (mWh)]]/1.5))</f>
-        <v>-</v>
-      </c>
-      <c r="S11" s="15" t="str">
+        <v>3000</v>
+      </c>
+      <c r="Q11" s="14">
+        <v>8</v>
+      </c>
+      <c r="R11" s="15">
+        <v>15.99</v>
+      </c>
+      <c r="S11" s="15">
         <f>IFERROR(Table35[[#This Row],[Package Price
 ($)]]/Table35[[#This Row],[Pkg Qty]],"")</f>
-        <v/>
-      </c>
-      <c r="T11" s="3" t="str">
+        <v>1.99875</v>
+      </c>
+      <c r="T11" s="3">
         <f>IFERROR(Table35[[#This Row],[Capacity (mAh)
 (Averaged)]]/Table35[[#This Row],[Price per battery
 ($)]],"")</f>
-        <v/>
+        <v>1721.5759849906192</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -2342,7 +2377,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="O2:P25">
+  <conditionalFormatting sqref="O2:O25">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -2367,7 +2402,7 @@
   <dimension ref="A1:T25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.42578125" style="7" customWidth="1"/>
     <col min="2" max="2" width="9.140625" style="7"/>
     <col min="3" max="3" width="12.28515625" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.140625" style="16" bestFit="1" customWidth="1"/>
@@ -2395,13 +2430,13 @@
         <v>24</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>8</v>
@@ -2413,51 +2448,51 @@
         <v>15</v>
       </c>
       <c r="I1" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J1" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q1" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="R1" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="S1" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="T1" s="8" t="s">
         <v>42</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="M1" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="O1" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="P1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q1" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="R1" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="S1" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="T1" s="8" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>19</v>
@@ -2531,7 +2566,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D3" s="4">
         <v>550</v>
@@ -2605,7 +2640,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D4" s="4">
         <v>750</v>
@@ -2679,7 +2714,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D5" s="4">
         <v>900</v>
@@ -2753,7 +2788,7 @@
         <v>6</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D6" s="4">
         <v>1875</v>
@@ -2821,13 +2856,13 @@
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D7" s="4">
         <v>1650</v>
@@ -2901,7 +2936,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D8" s="4">
         <v>1875</v>
@@ -2975,7 +3010,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D9" s="4">
         <v>1100</v>
@@ -3043,13 +3078,13 @@
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D10" s="4">
         <v>1800</v>
@@ -3747,7 +3782,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="O2:P25">
+  <conditionalFormatting sqref="O2:O25">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -3813,7 +3848,7 @@
     </row>
     <row r="8" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3"/>
